--- a/artfynd/A 24485-2026 artfynd.xlsx
+++ b/artfynd/A 24485-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103382226</v>
+        <v>114012156</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>768906.2902566134</v>
+        <v>768996</v>
       </c>
       <c r="R2" t="n">
-        <v>7525386.439992119</v>
+        <v>7525267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103382227</v>
+        <v>114012157</v>
       </c>
       <c r="B3" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>768930.7405037351</v>
+        <v>768976</v>
       </c>
       <c r="R3" t="n">
-        <v>7525338.529453618</v>
+        <v>7525259</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2022-08-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ruaridh Hägglund</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114012156</v>
+        <v>103382226</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>768996</v>
+        <v>768906</v>
       </c>
       <c r="R4" t="n">
-        <v>7525267</v>
+        <v>7525386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +967,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Ruaridh Hägglund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1013,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114012157</v>
+        <v>103382227</v>
       </c>
       <c r="B5" t="n">
-        <v>90258</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3242</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>768976</v>
+        <v>768931</v>
       </c>
       <c r="R5" t="n">
-        <v>7525259</v>
+        <v>7525338</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1068,111 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114012158</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hosiorinta, T lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>768917</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7525226</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-08-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ruaridh Hägglund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Torbjörn Josefsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 24485-2026 artfynd.xlsx
+++ b/artfynd/A 24485-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012157</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382226</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103382227</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114012158</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>